--- a/Post-processing.xlsx
+++ b/Post-processing.xlsx
@@ -536,11 +536,21 @@
       <c r="A14" s="1" t="n">
         <v>0.75</v>
       </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Bardock</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n">
         <v>0.7916666666666666</v>
       </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Bardock</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="n">
@@ -548,18 +558,13 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>spid</t>
+          <t>Bardock</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n">
         <v>0.875</v>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>spid</t>
-        </is>
       </c>
     </row>
     <row r="18">
